--- a/sheets/조재수대금교본/검수/어디로 갈거나-2.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 갈거나-2.xlsx
@@ -3974,7 +3974,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -4001,7 +4001,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ
+          <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
@@ -4016,49 +4016,21 @@
     </row>
     <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B4" s="21"/>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="23"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="90.2" customHeight="true">
@@ -4066,52 +4038,43 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∼
-‹</t>
+          <t xml:space="preserve">㴌∼</t>
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-Z</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -4146,11 +4109,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -4232,55 +4191,35 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="90.2" customHeight="true">
@@ -4308,8 +4247,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-Z</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -4351,11 +4289,7 @@
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -4364,11 +4298,7 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -4377,11 +4307,7 @@
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -4390,61 +4316,46 @@
         </is>
       </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G11" s="24"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="M11" s="24"/>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N11" s="21"/>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
@@ -4458,7 +4369,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄷ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -4471,7 +4382,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄷ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4484,7 +4395,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄷ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -4497,7 +4408,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄷ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4511,11 +4422,7 @@
     </row>
     <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
@@ -4523,24 +4430,16 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㴌
-汰∽</t>
+汰</t>
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4548,11 +4447,7 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
@@ -4570,49 +4465,24 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/어디로 갈거나-2.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 갈거나-2.xlsx
@@ -3974,7 +3974,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -4001,7 +4001,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰ㄷ
 –</t>
         </is>
       </c>
@@ -4016,21 +4016,49 @@
     </row>
     <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="90.2" customHeight="true">
@@ -4045,7 +4073,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -4055,7 +4083,12 @@
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+Z</t>
+        </is>
+      </c>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
@@ -4067,7 +4100,7 @@
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -4109,7 +4142,11 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -4247,7 +4284,8 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌
+Z</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -4289,7 +4327,11 @@
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -4298,7 +4340,11 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -4307,7 +4353,11 @@
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -4316,7 +4366,11 @@
         </is>
       </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="21"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="90.2" customHeight="true">
@@ -4330,7 +4384,7 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -4351,7 +4405,7 @@
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4369,7 +4423,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄷ</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -4382,7 +4436,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄷ</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4395,7 +4449,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄷ</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -4408,7 +4462,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄷ</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4422,7 +4476,11 @@
     </row>
     <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
-      <c r="B13" s="21"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
@@ -4430,16 +4488,24 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㴌
-汰</t>
+汰∽</t>
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4447,7 +4513,11 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/어디로 갈거나-2.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 갈거나-2.xlsx
@@ -3912,28 +3912,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4561,6 +4561,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>